--- a/참고사항/TimingChart.xlsx
+++ b/참고사항/TimingChart.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="129">
   <si>
     <t>실제값(예시)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -120,51 +120,196 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CTRL_BYTE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CTRL_BYTE_R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CTRL_BYTE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cmd ==  2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDR_H</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADDR_L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DATA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CTRL_BYTE_R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CTRL_BYTE_R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>READ_DATA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>IDLE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>IDLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>START</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CTRL_BYTE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>I2C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitTxRx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCL_LOW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDA_SETUP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCL_LOW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCL_HIGH</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteData</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOAD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WAIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LOAD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SHIFT_BIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(자동)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK_CHECK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DONE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(자동)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WAIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter == tLow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter == tsu(Data)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter == thigh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteStart == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteStart == 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitDone == 1</t>
+  </si>
+  <si>
+    <t>BitDone == 0</t>
+  </si>
+  <si>
+    <t>SdaOe = DriveEn</t>
   </si>
   <si>
     <t>busy = 0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>START</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CTRL_BYTE_R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CTRL_BYTE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cmd ==  2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADDR_H</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADDR_L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DATA</t>
+    <t>ACK == 1, ByteDone==1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 1, cmd == 0, ByteDone==1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 1, ByteDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REP_START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REP_START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 1, cmd == 1, ByteDone==1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 1, ByteDone==1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 0, ByteDone == 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -172,11 +317,159 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CTRL_BYTE_R</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CTRL_BYTE_R</t>
+    <t>busy = 1, nack_err = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 0 done =1, I2cStop = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK == 0, ByteDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = DriveEn, BitDone=1, SdaLatch = SdaIn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = DriveEn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitDone == 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitCount &gt; 0, BitDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitCount == 0, BitDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitDone == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WAIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCL_LOW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GEN_START</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I2cStop == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GEN_STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WAIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GEN_STOP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitStart == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>I2cStart == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter == tHD:STA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = 1, Sda = 0, BitDone = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter &lt; tHD:STA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = 1, Sda = 0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter == tSU:STO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = 0, Sda = 1, BitDone = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter &lt; tSU:STO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = 0, Sda = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter &lt; tLow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = DriveEn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter &lt; tsu(Data)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = DriveEn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>counter &lt; thigh</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SdaOe = DriveEn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitCount = 7, BitStart=1, DriveEn=rw==Write?1:0, reg = WriteData</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitStart = 1, reg = reg[6:0] &amp; SdaLatch, BtiCount - 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BitStart=1, reg = reg[6:0] &amp; SdaLatch, BtiCount - 1, DriveEn = rw==Write ? 0:1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ACK = SdaLatch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteDone = 1, ReadData = reg</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -184,355 +477,51 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>STOP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STOP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IDLE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Start == 0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I2C</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitTxRx</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SCL_LOW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SDA_SETUP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SCL_LOW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SCL_HIGH</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ByteData</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOAD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WAIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LOAD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SHIFT_BIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(자동)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACK_CHECK</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DONE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>(자동)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WAIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>counter == tLow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>counter == tsu(Data)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>counter == thigh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ByteStart == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ByteStart == 0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitDone == 1</t>
-  </si>
-  <si>
-    <t>BitDone == 0</t>
-  </si>
-  <si>
-    <t>cmd ==  0 or 1, ByteDone == 1, ACK == 1</t>
-  </si>
-  <si>
-    <t>SdaOe = DriveEn</t>
-  </si>
-  <si>
-    <t>Start == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>busy = 0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACK == 1, ByteDone==1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACK == 1, cmd == 0, ByteDone==1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACK == 1, ByteDone == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>REP_START</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>REP_START</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACK == 1, cmd == 1, ByteDone==1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACK == 1, ByteDone==1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>busy = 1, I2cStart = 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACK == 0, ByteDone == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>STOP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>busy = 1, nack_err = 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitDone == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>busy = 0 done =1, I2cStop = 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACK == 0, ByteDone == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SdaOe = DriveEn, BitDone=1, SdaLatch = SdaIn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SdaOe = DriveEn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitDone == 0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitCount &gt; 0, BitDone == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitCount == 0, BitDone == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitDone == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitDone == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WAIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SCL_LOW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GEN_START</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I2cStop == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GEN_STOP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WAIT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GEN_STOP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitStart == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>I2cStart == 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>counter == tHD:STA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SdaOe = 1, Sda = 0, BitDone = 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>counter &lt; tHD:STA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SdaOe = 1, Sda = 0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>counter == tSU:STO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SdaOe = 0, Sda = 1, BitDone = 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>counter &lt; tSU:STO</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SdaOe = 0, Sda = 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>counter &lt; tLow</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SdaOe = DriveEn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>counter &lt; tsu(Data)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SdaOe = DriveEn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>counter &lt; thigh</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SdaOe = DriveEn</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitCount = 7, BitStart=1, DriveEn=rw==Write?1:0, reg = WriteData</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitStart = 1, reg = reg[6:0] &amp; SdaLatch, BtiCount - 1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BitStart=1, reg = reg[6:0] &amp; SdaLatch, BtiCount - 1, DriveEn = rw==Write ? 0:1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ACK = SdaLatch</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ByteDone = 1, ReadData = reg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>busy = 1, WriteData = 0xA0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>busy = 1, WriteData = 0xA0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>busy = 1, WriteData = Addr[14:8]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>busy = 1, WriteData = addr[7:0]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>busy = 1, WriteData = WData</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>busy = 1, WriteData = addr[7:0]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>busy = 1, WriteData = 0xA1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>READ_DATA</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>busy = 1, Rdata = ReadData</t>
+    <t>Run == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ByteStart = 1, rw = 0, busy = 1, I2cStart = 1 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteDone == 1, ACK == 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, ByteStart = 1, rw = 0 WriteData = 0xA0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteStart = 1, WriteData = Addr[14:8], busy = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, ByteStart = 1, WriteData = addr[7:0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>busy = 1, ByteStart = 1, I2cStart = 1, WriteData = addr[7:0]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteStart = 1, busy = 1, WriteData = WData</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rw = 1, ByteStart = 1, busy = 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rw = 0, ByteStart = 1, busy = 1, WriteData = 0xA1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ByteStart = 1, rw = 1, busy = 1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -759,22 +748,22 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1353,8 +1342,8 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>534623</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>162269</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>137421</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1430,7 +1419,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>624178</xdr:colOff>
       <xdr:row>81</xdr:row>
-      <xdr:rowOff>68687</xdr:rowOff>
+      <xdr:rowOff>68686</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1467,8 +1456,8 @@
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>448235</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>124432</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>116150</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1499,8 +1488,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="V7:Y26" headerRowDxfId="38" dataDxfId="37" totalsRowDxfId="35" tableBorderDxfId="36" totalsRowBorderDxfId="34">
-  <autoFilter ref="V7:Y26"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="V7:Y25" headerRowDxfId="38" dataDxfId="37" totalsRowDxfId="35" tableBorderDxfId="36" totalsRowBorderDxfId="34">
+  <autoFilter ref="V7:Y25"/>
   <tableColumns count="4">
     <tableColumn id="1" name="현재 상태" totalsRowLabel="요약" dataDxfId="33" totalsRowDxfId="32"/>
     <tableColumn id="2" name="입력조건" dataDxfId="31" totalsRowDxfId="30"/>
@@ -1512,8 +1501,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표1_3" displayName="표1_3" ref="V29:Y43" headerRowDxfId="25" dataDxfId="24" totalsRowDxfId="22" tableBorderDxfId="23" totalsRowBorderDxfId="21">
-  <autoFilter ref="V29:Y43"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="표1_3" displayName="표1_3" ref="V28:Y42" headerRowDxfId="25" dataDxfId="24" totalsRowDxfId="22" tableBorderDxfId="23" totalsRowBorderDxfId="21">
+  <autoFilter ref="V28:Y42"/>
   <tableColumns count="4">
     <tableColumn id="1" name="현재 상태" totalsRowLabel="요약" dataDxfId="20" totalsRowDxfId="19"/>
     <tableColumn id="2" name="입력조건" dataDxfId="18" totalsRowDxfId="17"/>
@@ -1525,8 +1514,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="표1_34" displayName="표1_34" ref="V46:Y55" headerRowDxfId="12" dataDxfId="11" totalsRowDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
-  <autoFilter ref="V46:Y55"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="표1_34" displayName="표1_34" ref="V45:Y54" headerRowDxfId="12" dataDxfId="11" totalsRowDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="V45:Y54"/>
   <tableColumns count="4">
     <tableColumn id="1" name="현재 상태" totalsRowLabel="요약" dataDxfId="7" totalsRowDxfId="6"/>
     <tableColumn id="2" name="입력조건" dataDxfId="5" totalsRowDxfId="4"/>
@@ -1888,7 +1877,7 @@
     </row>
     <row r="6" spans="2:25" x14ac:dyDescent="0.3">
       <c r="V6" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="2:25" x14ac:dyDescent="0.3">
@@ -1910,153 +1899,153 @@
         <v>26</v>
       </c>
       <c r="W8" s="9" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y8" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="2:25" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="2:25" ht="33" x14ac:dyDescent="0.3">
       <c r="V9" s="9" t="s">
         <v>27</v>
       </c>
       <c r="W9" s="9" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="X9" s="9" t="s">
         <v>28</v>
       </c>
       <c r="Y9" s="9" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.3">
       <c r="V10" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="W10" s="9" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="X10" s="9" t="s">
         <v>30</v>
       </c>
       <c r="Y10" s="9" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="2:25" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="2:25" ht="33" x14ac:dyDescent="0.3">
       <c r="V11" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="X11" s="9" t="s">
         <v>33</v>
       </c>
       <c r="Y11" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" ht="33" x14ac:dyDescent="0.3">
+      <c r="V12" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="W12" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="X12" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y12" s="9" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" ht="33" x14ac:dyDescent="0.3">
+      <c r="V13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="W13" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="X13" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y13" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" ht="33" x14ac:dyDescent="0.3">
+      <c r="V14" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="W14" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X14" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y14" s="9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="V12" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="W12" s="9" t="s">
+    <row r="15" spans="2:25" ht="33" x14ac:dyDescent="0.3">
+      <c r="V15" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="W15" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="X12" s="9" t="s">
+      <c r="X15" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="Y12" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="V13" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="W13" s="9" t="s">
+      <c r="Y15" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="V16" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="W16" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="X16" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y16" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="33" x14ac:dyDescent="0.3">
+      <c r="V17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="W17" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="X13" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y13" s="9" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="V14" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="W14" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="X14" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="Y14" s="9" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="V15" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="W15" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="X15" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y15" s="9" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="V16" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="X16" s="11" t="s">
+      <c r="X17" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="Y16" s="9" t="s">
+      <c r="Y17" s="9" t="s">
         <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="V17" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W17" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="X17" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="Y17" s="9" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="V18" s="11" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="W18" s="11" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="X18" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y18" s="9" t="s">
-        <v>129</v>
+        <v>40</v>
+      </c>
+      <c r="Y18" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
@@ -2082,16 +2071,16 @@
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
       <c r="V19" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="W19" s="11" t="s">
-        <v>80</v>
+        <v>41</v>
+      </c>
+      <c r="W19" s="9" t="s">
+        <v>87</v>
       </c>
       <c r="X19" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Y19" s="11" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
@@ -2116,17 +2105,17 @@
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
       <c r="U20" s="4"/>
-      <c r="V20" s="11" t="s">
-        <v>44</v>
+      <c r="V20" s="9" t="s">
+        <v>31</v>
       </c>
       <c r="W20" s="9" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="X20" s="11" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="Y20" s="11" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
@@ -2152,16 +2141,16 @@
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
       <c r="V21" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="W21" s="9" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="Y21" s="11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
@@ -2187,16 +2176,16 @@
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
       <c r="V22" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="W22" s="9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="Y22" s="11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
@@ -2222,16 +2211,16 @@
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
       <c r="V23" s="9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="W23" s="9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="Y23" s="11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
@@ -2256,17 +2245,17 @@
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
       <c r="U24" s="4"/>
-      <c r="V24" s="9" t="s">
+      <c r="V24" s="11" t="s">
         <v>38</v>
       </c>
       <c r="W24" s="9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="Y24" s="11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
@@ -2292,16 +2281,16 @@
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
       <c r="V25" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="W25" s="9" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="X25" s="11" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="Y25" s="11" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
@@ -2326,18 +2315,10 @@
       <c r="S26" s="4"/>
       <c r="T26" s="4"/>
       <c r="U26" s="4"/>
-      <c r="V26" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="W26" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="X26" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y26" s="11" t="s">
-        <v>84</v>
-      </c>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
@@ -2361,7 +2342,9 @@
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
-      <c r="V27" s="4"/>
+      <c r="V27" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="W27" s="4"/>
       <c r="X27" s="4"/>
       <c r="Y27" s="4"/>
@@ -2388,12 +2371,18 @@
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
-      <c r="V28" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="W28" s="4"/>
-      <c r="X28" s="4"/>
-      <c r="Y28" s="4"/>
+      <c r="V28" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="W28" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="X28" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y28" s="10" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
@@ -2417,18 +2406,16 @@
       <c r="S29" s="4"/>
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
-      <c r="V29" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="W29" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="X29" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y29" s="10" t="s">
-        <v>22</v>
-      </c>
+      <c r="V29" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="W29" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="X29" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y29" s="13"/>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
@@ -2453,13 +2440,13 @@
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
       <c r="V30" s="13" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="W30" s="13" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="X30" s="13" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="Y30" s="13"/>
     </row>
@@ -2486,78 +2473,80 @@
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
       <c r="V31" s="13" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="W31" s="13" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="X31" s="13" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="Y31" s="13"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="V32" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="W32" s="13" t="s">
-        <v>98</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="W32" s="13"/>
       <c r="X32" s="13" t="s">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="Y32" s="13"/>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="V33" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="W33" s="13"/>
+        <v>90</v>
+      </c>
+      <c r="W33" s="13" t="s">
+        <v>97</v>
+      </c>
       <c r="X33" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y33" s="13"/>
+        <v>93</v>
+      </c>
+      <c r="Y33" s="13" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="V34" s="13" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="W34" s="13" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="X34" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y34" s="13" t="s">
         <v>100</v>
-      </c>
-      <c r="Y34" s="13" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="V35" s="13" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="W35" s="13" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="X35" s="13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="Y35" s="13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="V36" s="13" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="W36" s="13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="X36" s="13" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="Y36" s="13" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -2582,432 +2571,424 @@
       <c r="Q37" s="3"/>
       <c r="R37" s="2"/>
       <c r="S37" s="3"/>
-      <c r="V37" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="W37" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="X37" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y37" s="13" t="s">
-        <v>111</v>
+      <c r="V37" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="W37" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="X37" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y37" s="9" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17" t="s">
+      <c r="B38" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
+      <c r="O38" s="14"/>
+      <c r="P38" s="14"/>
+      <c r="Q38" s="14"/>
+      <c r="R38" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="S38" s="18"/>
+      <c r="S38" s="15"/>
       <c r="V38" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="W38" s="9" t="s">
-        <v>63</v>
+        <v>105</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="Y38" s="9" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="16">
         <v>1</v>
       </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14">
-        <v>0</v>
-      </c>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14">
+      <c r="C39" s="16"/>
+      <c r="D39" s="16">
+        <v>0</v>
+      </c>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16">
         <v>1</v>
       </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14">
-        <v>0</v>
-      </c>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14">
-        <v>0</v>
-      </c>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14">
-        <v>0</v>
-      </c>
-      <c r="M39" s="14"/>
-      <c r="N39" s="14">
-        <v>0</v>
-      </c>
-      <c r="O39" s="14"/>
-      <c r="P39" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q39" s="14"/>
-      <c r="R39" s="14" t="s">
+      <c r="G39" s="16"/>
+      <c r="H39" s="16">
+        <v>0</v>
+      </c>
+      <c r="I39" s="16"/>
+      <c r="J39" s="16">
+        <v>0</v>
+      </c>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16">
+        <v>0</v>
+      </c>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16">
+        <v>0</v>
+      </c>
+      <c r="O39" s="16"/>
+      <c r="P39" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="16"/>
+      <c r="R39" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="S39" s="14"/>
+      <c r="S39" s="16"/>
       <c r="V39" s="9" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="W39" s="9" t="s">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Y39" s="9" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B40" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14" t="s">
+      <c r="C40" s="16"/>
+      <c r="D40" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14" t="s">
+      <c r="E40" s="16"/>
+      <c r="F40" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14" t="s">
+      <c r="G40" s="16"/>
+      <c r="H40" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14" t="s">
+      <c r="I40" s="16"/>
+      <c r="J40" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14" t="s">
+      <c r="K40" s="16"/>
+      <c r="L40" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14" t="s">
+      <c r="M40" s="16"/>
+      <c r="N40" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="O40" s="14"/>
-      <c r="P40" s="14" t="s">
+      <c r="O40" s="16"/>
+      <c r="P40" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="Q40" s="14"/>
-      <c r="R40" s="14" t="s">
+      <c r="Q40" s="16"/>
+      <c r="R40" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="S40" s="14"/>
+      <c r="S40" s="16"/>
       <c r="V40" s="9" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="W40" s="9" t="s">
-        <v>64</v>
+        <v>107</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="Y40" s="9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14" t="s">
+      <c r="C41" s="16"/>
+      <c r="D41" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14" t="s">
+      <c r="E41" s="16"/>
+      <c r="F41" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14" t="s">
+      <c r="G41" s="16"/>
+      <c r="H41" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14" t="s">
+      <c r="I41" s="16"/>
+      <c r="J41" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14" t="s">
+      <c r="K41" s="16"/>
+      <c r="L41" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14" t="s">
+      <c r="M41" s="16"/>
+      <c r="N41" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="O41" s="14"/>
-      <c r="P41" s="14" t="s">
+      <c r="O41" s="16"/>
+      <c r="P41" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="Q41" s="14"/>
-      <c r="R41" s="14" t="s">
+      <c r="Q41" s="16"/>
+      <c r="R41" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="S41" s="14"/>
+      <c r="S41" s="16"/>
       <c r="V41" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="W41" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="X41" s="9" t="s">
-        <v>50</v>
+        <v>61</v>
+      </c>
+      <c r="X41" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="Y41" s="9" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" ht="33.75" thickBot="1" x14ac:dyDescent="0.35">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="14">
-        <v>0</v>
-      </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14">
-        <v>0</v>
-      </c>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14">
+      <c r="B42" s="16">
+        <v>0</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16">
+        <v>0</v>
+      </c>
+      <c r="E42" s="16"/>
+      <c r="F42" s="16">
         <v>1</v>
       </c>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14">
+      <c r="G42" s="16"/>
+      <c r="H42" s="16">
         <v>1</v>
       </c>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14">
+      <c r="I42" s="16"/>
+      <c r="J42" s="16">
         <v>1</v>
       </c>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14">
+      <c r="K42" s="16"/>
+      <c r="L42" s="16">
         <v>1</v>
       </c>
-      <c r="M42" s="14"/>
-      <c r="N42" s="14">
-        <v>0</v>
-      </c>
-      <c r="O42" s="14"/>
-      <c r="P42" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="14"/>
-      <c r="R42" s="14" t="s">
+      <c r="M42" s="16"/>
+      <c r="N42" s="16">
+        <v>0</v>
+      </c>
+      <c r="O42" s="16"/>
+      <c r="P42" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="16"/>
+      <c r="R42" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="S42" s="14"/>
+      <c r="S42" s="16"/>
       <c r="T42" s="6" t="s">
         <v>17</v>
       </c>
       <c r="V42" s="9" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="W42" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="X42" s="13" t="s">
-        <v>55</v>
+        <v>109</v>
+      </c>
+      <c r="X42" s="9" t="s">
+        <v>48</v>
       </c>
       <c r="Y42" s="9" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="V43" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="W43" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="X43" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="Y43" s="9" t="s">
-        <v>117</v>
-      </c>
+      <c r="V43" s="11"/>
+      <c r="W43" s="11"/>
+      <c r="X43" s="11"/>
+      <c r="Y43" s="11"/>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="V44" s="11"/>
+      <c r="V44" s="11" t="s">
+        <v>49</v>
+      </c>
       <c r="W44" s="11"/>
       <c r="X44" s="11"/>
       <c r="Y44" s="11"/>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="V45" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="W45" s="11"/>
-      <c r="X45" s="11"/>
-      <c r="Y45" s="11"/>
+      <c r="V45" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="W45" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="X45" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y45" s="10" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="V46" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="W46" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="X46" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y46" s="10" t="s">
-        <v>22</v>
-      </c>
+      <c r="V46" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="W46" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="X46" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y46" s="9"/>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="V47" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="W47" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="X47" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y47" s="9"/>
+    </row>
+    <row r="48" spans="1:25" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="V48" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="W48" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="X48" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y48" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V49" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="W49" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="X49" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y49" s="9"/>
+    </row>
+    <row r="50" spans="1:25" ht="33" x14ac:dyDescent="0.3">
+      <c r="V50" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="W50" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="X50" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y50" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="V51" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="W51" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="X51" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="W47" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="X47" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y47" s="9"/>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="V48" s="9" t="s">
+      <c r="Y51" s="9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="V52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="W48" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="X48" s="9" t="s">
+      <c r="W52" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="X52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="Y48" s="9"/>
-    </row>
-    <row r="49" spans="1:25" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="V49" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="W49" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="X49" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y49" s="9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="V50" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="W50" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="X50" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y50" s="9"/>
-    </row>
-    <row r="51" spans="1:25" ht="33" x14ac:dyDescent="0.3">
-      <c r="V51" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="W51" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="X51" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y51" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="V52" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="W52" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="X52" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y52" s="9" t="s">
-        <v>120</v>
-      </c>
+      <c r="Y52" s="9"/>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="V53" s="9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="W53" s="9" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="X53" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y53" s="9"/>
+        <v>56</v>
+      </c>
+      <c r="Y53" s="9" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="V54" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="W54" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="X54" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y54" s="9" t="s">
-        <v>121</v>
+        <v>56</v>
+      </c>
+      <c r="W54" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="X54" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y54" s="12" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="V55" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="W55" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="X55" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y55" s="12" t="s">
-        <v>122</v>
-      </c>
+      <c r="V55" s="12"/>
+      <c r="W55" s="12"/>
+      <c r="X55" s="12"/>
+      <c r="Y55" s="12"/>
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="V56" s="12"/>
@@ -3021,12 +3002,7 @@
       <c r="X57" s="12"/>
       <c r="Y57" s="12"/>
     </row>
-    <row r="58" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="V58" s="12"/>
-      <c r="W58" s="12"/>
-      <c r="X58" s="12"/>
-      <c r="Y58" s="12"/>
-    </row>
+    <row r="58" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="59" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>16</v>
@@ -3054,258 +3030,258 @@
       <c r="A60" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B60" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
-      <c r="H60" s="17"/>
-      <c r="I60" s="17"/>
-      <c r="J60" s="17"/>
-      <c r="K60" s="17"/>
-      <c r="L60" s="17"/>
-      <c r="M60" s="17"/>
-      <c r="N60" s="17"/>
-      <c r="O60" s="17"/>
-      <c r="P60" s="17"/>
-      <c r="Q60" s="17"/>
-      <c r="R60" s="17" t="s">
+      <c r="B60" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+      <c r="M60" s="14"/>
+      <c r="N60" s="14"/>
+      <c r="O60" s="14"/>
+      <c r="P60" s="14"/>
+      <c r="Q60" s="14"/>
+      <c r="R60" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="S60" s="18"/>
+      <c r="S60" s="15"/>
     </row>
     <row r="61" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B61" s="14">
+      <c r="B61" s="16">
         <v>1</v>
       </c>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14">
-        <v>0</v>
-      </c>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14">
+      <c r="C61" s="16"/>
+      <c r="D61" s="16">
+        <v>0</v>
+      </c>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16">
         <v>1</v>
       </c>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14">
-        <v>0</v>
-      </c>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14">
-        <v>0</v>
-      </c>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14">
-        <v>0</v>
-      </c>
-      <c r="M61" s="14"/>
-      <c r="N61" s="14">
-        <v>0</v>
-      </c>
-      <c r="O61" s="14"/>
-      <c r="P61" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="14"/>
-      <c r="R61" s="14" t="s">
+      <c r="G61" s="16"/>
+      <c r="H61" s="16">
+        <v>0</v>
+      </c>
+      <c r="I61" s="16"/>
+      <c r="J61" s="16">
+        <v>0</v>
+      </c>
+      <c r="K61" s="16"/>
+      <c r="L61" s="16">
+        <v>0</v>
+      </c>
+      <c r="M61" s="16"/>
+      <c r="N61" s="16">
+        <v>0</v>
+      </c>
+      <c r="O61" s="16"/>
+      <c r="P61" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="16"/>
+      <c r="R61" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="S61" s="14"/>
+      <c r="S61" s="16"/>
     </row>
     <row r="62" spans="1:25" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14" t="s">
+      <c r="C62" s="16"/>
+      <c r="D62" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14" t="s">
+      <c r="E62" s="16"/>
+      <c r="F62" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14" t="s">
+      <c r="G62" s="16"/>
+      <c r="H62" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14" t="s">
+      <c r="I62" s="16"/>
+      <c r="J62" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14" t="s">
+      <c r="K62" s="16"/>
+      <c r="L62" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M62" s="14"/>
-      <c r="N62" s="14" t="s">
+      <c r="M62" s="16"/>
+      <c r="N62" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="O62" s="14"/>
-      <c r="P62" s="14" t="s">
+      <c r="O62" s="16"/>
+      <c r="P62" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="Q62" s="14"/>
-      <c r="R62" s="14" t="s">
+      <c r="Q62" s="16"/>
+      <c r="R62" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="S62" s="14"/>
+      <c r="S62" s="16"/>
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B63" s="19" t="s">
+      <c r="B63" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C63" s="19"/>
-      <c r="D63" s="19" t="s">
+      <c r="C63" s="17"/>
+      <c r="D63" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="E63" s="19"/>
-      <c r="F63" s="19" t="s">
+      <c r="E63" s="17"/>
+      <c r="F63" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G63" s="19"/>
-      <c r="H63" s="19" t="s">
+      <c r="G63" s="17"/>
+      <c r="H63" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="I63" s="19"/>
-      <c r="J63" s="19" t="s">
+      <c r="I63" s="17"/>
+      <c r="J63" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="K63" s="19"/>
-      <c r="L63" s="19" t="s">
+      <c r="K63" s="17"/>
+      <c r="L63" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="M63" s="19"/>
-      <c r="N63" s="19" t="s">
+      <c r="M63" s="17"/>
+      <c r="N63" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="O63" s="19"/>
-      <c r="P63" s="19" t="s">
+      <c r="O63" s="17"/>
+      <c r="P63" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="Q63" s="19"/>
-      <c r="R63" s="19" t="s">
+      <c r="Q63" s="17"/>
+      <c r="R63" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="S63" s="19"/>
+      <c r="S63" s="17"/>
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B64" s="16" t="s">
+      <c r="B64" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C64" s="16"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
-      <c r="H64" s="16"/>
-      <c r="I64" s="16"/>
-      <c r="J64" s="16"/>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="16"/>
-      <c r="O64" s="16"/>
-      <c r="P64" s="16"/>
-      <c r="Q64" s="16"/>
-      <c r="R64" s="16"/>
-      <c r="S64" s="16"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="19"/>
+      <c r="F64" s="19"/>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19"/>
+      <c r="K64" s="19"/>
+      <c r="L64" s="19"/>
+      <c r="M64" s="19"/>
+      <c r="N64" s="19"/>
+      <c r="O64" s="19"/>
+      <c r="P64" s="19"/>
+      <c r="Q64" s="19"/>
+      <c r="R64" s="19"/>
+      <c r="S64" s="19"/>
     </row>
     <row r="65" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B65" s="15">
+      <c r="B65" s="18">
         <v>1</v>
       </c>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15">
-        <v>0</v>
-      </c>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15">
+      <c r="C65" s="18"/>
+      <c r="D65" s="18">
+        <v>0</v>
+      </c>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18">
         <v>1</v>
       </c>
-      <c r="G65" s="15"/>
-      <c r="H65" s="15">
-        <v>0</v>
-      </c>
-      <c r="I65" s="15"/>
-      <c r="J65" s="15">
-        <v>0</v>
-      </c>
-      <c r="K65" s="15"/>
-      <c r="L65" s="15">
-        <v>0</v>
-      </c>
-      <c r="M65" s="15"/>
-      <c r="N65" s="15">
-        <v>0</v>
-      </c>
-      <c r="O65" s="15"/>
-      <c r="P65" s="15">
+      <c r="G65" s="18"/>
+      <c r="H65" s="18">
+        <v>0</v>
+      </c>
+      <c r="I65" s="18"/>
+      <c r="J65" s="18">
+        <v>0</v>
+      </c>
+      <c r="K65" s="18"/>
+      <c r="L65" s="18">
+        <v>0</v>
+      </c>
+      <c r="M65" s="18"/>
+      <c r="N65" s="18">
+        <v>0</v>
+      </c>
+      <c r="O65" s="18"/>
+      <c r="P65" s="18">
         <v>1</v>
       </c>
-      <c r="Q65" s="15"/>
-      <c r="R65" s="15" t="s">
+      <c r="Q65" s="18"/>
+      <c r="R65" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="S65" s="15"/>
+      <c r="S65" s="18"/>
     </row>
     <row r="66" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B66" s="14">
-        <v>0</v>
-      </c>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14">
-        <v>0</v>
-      </c>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14">
+      <c r="B66" s="16">
+        <v>0</v>
+      </c>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16">
+        <v>0</v>
+      </c>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16">
         <v>1</v>
       </c>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14">
+      <c r="G66" s="16"/>
+      <c r="H66" s="16">
         <v>1</v>
       </c>
-      <c r="I66" s="14"/>
-      <c r="J66" s="14">
+      <c r="I66" s="16"/>
+      <c r="J66" s="16">
         <v>1</v>
       </c>
-      <c r="K66" s="14"/>
-      <c r="L66" s="14">
+      <c r="K66" s="16"/>
+      <c r="L66" s="16">
         <v>1</v>
       </c>
-      <c r="M66" s="14"/>
-      <c r="N66" s="14">
-        <v>0</v>
-      </c>
-      <c r="O66" s="14"/>
-      <c r="P66" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="14"/>
-      <c r="R66" s="14" t="s">
+      <c r="M66" s="16"/>
+      <c r="N66" s="16">
+        <v>0</v>
+      </c>
+      <c r="O66" s="16"/>
+      <c r="P66" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="16"/>
+      <c r="R66" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="S66" s="14"/>
+      <c r="S66" s="16"/>
       <c r="T66" s="6" t="s">
         <v>17</v>
       </c>
@@ -3354,189 +3330,125 @@
       <c r="A84" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B84" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="17"/>
-      <c r="G84" s="17"/>
-      <c r="H84" s="17"/>
-      <c r="I84" s="17"/>
-      <c r="J84" s="17"/>
-      <c r="K84" s="17"/>
-      <c r="L84" s="17"/>
-      <c r="M84" s="17"/>
-      <c r="N84" s="17"/>
-      <c r="O84" s="17"/>
-      <c r="P84" s="17"/>
-      <c r="Q84" s="17"/>
-      <c r="R84" s="17" t="s">
+      <c r="B84" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C84" s="14"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
+      <c r="G84" s="14"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="14"/>
+      <c r="K84" s="14"/>
+      <c r="L84" s="14"/>
+      <c r="M84" s="14"/>
+      <c r="N84" s="14"/>
+      <c r="O84" s="14"/>
+      <c r="P84" s="14"/>
+      <c r="Q84" s="14"/>
+      <c r="R84" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="S84" s="18"/>
+      <c r="S84" s="15"/>
     </row>
     <row r="85" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B85" s="14">
+      <c r="B85" s="16">
         <v>1</v>
       </c>
-      <c r="C85" s="14"/>
-      <c r="D85" s="14">
-        <v>0</v>
-      </c>
-      <c r="E85" s="14"/>
-      <c r="F85" s="14">
+      <c r="C85" s="16"/>
+      <c r="D85" s="16">
+        <v>0</v>
+      </c>
+      <c r="E85" s="16"/>
+      <c r="F85" s="16">
         <v>1</v>
       </c>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14">
-        <v>0</v>
-      </c>
-      <c r="I85" s="14"/>
-      <c r="J85" s="14">
-        <v>0</v>
-      </c>
-      <c r="K85" s="14"/>
-      <c r="L85" s="14">
-        <v>0</v>
-      </c>
-      <c r="M85" s="14"/>
-      <c r="N85" s="14">
-        <v>0</v>
-      </c>
-      <c r="O85" s="14"/>
-      <c r="P85" s="14">
+      <c r="G85" s="16"/>
+      <c r="H85" s="16">
+        <v>0</v>
+      </c>
+      <c r="I85" s="16"/>
+      <c r="J85" s="16">
+        <v>0</v>
+      </c>
+      <c r="K85" s="16"/>
+      <c r="L85" s="16">
+        <v>0</v>
+      </c>
+      <c r="M85" s="16"/>
+      <c r="N85" s="16">
+        <v>0</v>
+      </c>
+      <c r="O85" s="16"/>
+      <c r="P85" s="16">
         <v>1</v>
       </c>
-      <c r="Q85" s="14"/>
-      <c r="R85" s="14" t="s">
+      <c r="Q85" s="16"/>
+      <c r="R85" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="S85" s="14"/>
+      <c r="S85" s="16"/>
     </row>
     <row r="86" spans="1:20" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B86" s="14">
-        <v>0</v>
-      </c>
-      <c r="C86" s="14"/>
-      <c r="D86" s="14">
-        <v>0</v>
-      </c>
-      <c r="E86" s="14"/>
-      <c r="F86" s="14">
+      <c r="B86" s="16">
+        <v>0</v>
+      </c>
+      <c r="C86" s="16"/>
+      <c r="D86" s="16">
+        <v>0</v>
+      </c>
+      <c r="E86" s="16"/>
+      <c r="F86" s="16">
         <v>1</v>
       </c>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14">
+      <c r="G86" s="16"/>
+      <c r="H86" s="16">
         <v>1</v>
       </c>
-      <c r="I86" s="14"/>
-      <c r="J86" s="14">
+      <c r="I86" s="16"/>
+      <c r="J86" s="16">
         <v>1</v>
       </c>
-      <c r="K86" s="14"/>
-      <c r="L86" s="14">
+      <c r="K86" s="16"/>
+      <c r="L86" s="16">
         <v>1</v>
       </c>
-      <c r="M86" s="14"/>
-      <c r="N86" s="14">
-        <v>0</v>
-      </c>
-      <c r="O86" s="14"/>
-      <c r="P86" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="14"/>
-      <c r="R86" s="14" t="s">
+      <c r="M86" s="16"/>
+      <c r="N86" s="16">
+        <v>0</v>
+      </c>
+      <c r="O86" s="16"/>
+      <c r="P86" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="16"/>
+      <c r="R86" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="S86" s="14"/>
+      <c r="S86" s="16"/>
       <c r="T86" s="6" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="106">
-    <mergeCell ref="R38:S38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="J40:K40"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="P40:Q40"/>
-    <mergeCell ref="B38:Q38"/>
-    <mergeCell ref="R40:S40"/>
-    <mergeCell ref="R41:S41"/>
-    <mergeCell ref="R42:S42"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="R39:S39"/>
-    <mergeCell ref="B60:Q60"/>
-    <mergeCell ref="R60:S60"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="J41:K41"/>
-    <mergeCell ref="J42:K42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="N61:O61"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="R61:S61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="J62:K62"/>
-    <mergeCell ref="L62:M62"/>
-    <mergeCell ref="N62:O62"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="D61:E61"/>
-    <mergeCell ref="F61:G61"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="J61:K61"/>
-    <mergeCell ref="L61:M61"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="R63:S63"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="R62:S62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="J63:K63"/>
-    <mergeCell ref="L63:M63"/>
-    <mergeCell ref="N63:O63"/>
-    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="H86:I86"/>
+    <mergeCell ref="J86:K86"/>
+    <mergeCell ref="L86:M86"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="R86:S86"/>
     <mergeCell ref="N85:O85"/>
     <mergeCell ref="P85:Q85"/>
     <mergeCell ref="R85:S85"/>
@@ -3561,15 +3473,79 @@
     <mergeCell ref="N66:O66"/>
     <mergeCell ref="P66:Q66"/>
     <mergeCell ref="R66:S66"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="J86:K86"/>
-    <mergeCell ref="L86:M86"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="R86:S86"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="D66:E66"/>
+    <mergeCell ref="F66:G66"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="J66:K66"/>
+    <mergeCell ref="L66:M66"/>
+    <mergeCell ref="R63:S63"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="R62:S62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="J63:K63"/>
+    <mergeCell ref="L63:M63"/>
+    <mergeCell ref="N63:O63"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="R61:S61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="J62:K62"/>
+    <mergeCell ref="L62:M62"/>
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="D61:E61"/>
+    <mergeCell ref="F61:G61"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="J61:K61"/>
+    <mergeCell ref="L61:M61"/>
+    <mergeCell ref="R41:S41"/>
+    <mergeCell ref="R42:S42"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="R39:S39"/>
+    <mergeCell ref="B60:Q60"/>
+    <mergeCell ref="R60:S60"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="J41:K41"/>
+    <mergeCell ref="J42:K42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="R38:S38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="J40:K40"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="B38:Q38"/>
+    <mergeCell ref="R40:S40"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
